--- a/1. Database Design/Java25 Quyen Phan Database Design.xlsx
+++ b/1. Database Design/Java25 Quyen Phan Database Design.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java25\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A63AFD7-78A1-4A98-96F5-DD057377DBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070D2665-7CA5-4612-8AD4-8471397BB613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21120" tabRatio="588" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21120" tabRatio="588" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
     <sheet name="2. Mô hình logic" sheetId="5" r:id="rId2"/>
     <sheet name="3. Mô hình quan hệ" sheetId="6" r:id="rId3"/>
     <sheet name="4. Cơ sở dữ liệu" sheetId="7" r:id="rId4"/>
+    <sheet name="5. Test Data" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -665,7 +666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{37A6BE56-4EBA-4081-9A2F-AA7326C00113}">
+    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{A036C54C-7EDB-41D8-91AC-507C229652DF}">
       <text>
         <r>
           <rPr>
@@ -885,8 +886,307 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Quyen Ngoc Phan</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{7622DD86-15F6-4FF0-B2BF-F30B7EB0EB62}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Có thể trùng tên mặt hàng
+Để =&gt;2 mặt hàng cùng nhưng có màu sắc &amp;| chất liệu khác nhau thì xem như là 2 mặt hàng khác nhau</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{289CA930-5ADB-4E42-AB07-811D1D77C669}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Thuộc tính dẫn xuất</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{9018F1BA-E8EB-41CD-9073-D2DCC73D94CC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Chất liệu</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{0FEE9119-3B4B-47DC-9C38-BE337E7960C3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{42186E77-7C20-45FA-9C2D-570CF4B24C6D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{3C3B23AD-E39C-44A2-8693-8EA0423FF77D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1 active || inactive</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0" shapeId="0" xr:uid="{170E7888-5562-4473-A483-1A17D519C33E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+not nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{45228BC8-E373-4D56-ACB6-73CE1386D192}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+dmy hms</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J28" authorId="0" shapeId="0" xr:uid="{D0FBB0E2-3C54-4F6C-9830-8CC2256AB551}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+dmy</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{D62C5B83-3624-45E1-B330-652006DD1EDC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Chi tiết nhập hàng cho mặt hàng để quản lý lịch sử giá mua</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L59" authorId="0" shapeId="0" xr:uid="{F3CD418B-5CD0-4D2F-BBE6-8E2FCB89706E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+d/m/y h:m:s</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K68" authorId="0" shapeId="0" xr:uid="{37A6BE56-4EBA-4081-9A2F-AA7326C00113}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Thời gian cập nhật trạng thái đơn hàng</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="502">
   <si>
     <t>MatHang</t>
   </si>
@@ -2190,9 +2490,6 @@
     <t>PK FK</t>
   </si>
   <si>
-    <t>C06_DELIVERY_FEE</t>
-  </si>
-  <si>
     <t>T07_BILL</t>
   </si>
   <si>
@@ -2202,9 +2499,6 @@
     <t>C07_ORDER_ID</t>
   </si>
   <si>
-    <t>C10_TOTAL_OF_MONEY</t>
-  </si>
-  <si>
     <t>T90_PAYMENT_METHOD</t>
   </si>
   <si>
@@ -2266,13 +2560,495 @@
   </si>
   <si>
     <t>C05_PROVIDER_TAX_PCT</t>
+  </si>
+  <si>
+    <t>Áo 1</t>
+  </si>
+  <si>
+    <t>Áo 2</t>
+  </si>
+  <si>
+    <t>Áo 3</t>
+  </si>
+  <si>
+    <t>Quần 4</t>
+  </si>
+  <si>
+    <t>Quần 5</t>
+  </si>
+  <si>
+    <t>Giày 6</t>
+  </si>
+  <si>
+    <t>Giày 7</t>
+  </si>
+  <si>
+    <t>Giày 8</t>
+  </si>
+  <si>
+    <t>Giày 9</t>
+  </si>
+  <si>
+    <t>Giày 10</t>
+  </si>
+  <si>
+    <t>Giép 11</t>
+  </si>
+  <si>
+    <t>Áo 12</t>
+  </si>
+  <si>
+    <t>Giép 13</t>
+  </si>
+  <si>
+    <t>Mũ 14</t>
+  </si>
+  <si>
+    <t>Mũ 15</t>
+  </si>
+  <si>
+    <t>Thắt lưng 16</t>
+  </si>
+  <si>
+    <t>Thắt lưng 17</t>
+  </si>
+  <si>
+    <t>Mũ 18</t>
+  </si>
+  <si>
+    <t>Túi xách 1</t>
+  </si>
+  <si>
+    <t>Túi xách 2</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>BLUE</t>
+  </si>
+  <si>
+    <t>BLACK</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>ORIGIN</t>
+  </si>
+  <si>
+    <t>GRAY</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Giày</t>
+  </si>
+  <si>
+    <t>Dép</t>
+  </si>
+  <si>
+    <t>Túi xách</t>
+  </si>
+  <si>
+    <t>Size 'S' cho Nữ</t>
+  </si>
+  <si>
+    <t>Size 'M' cho Nữ</t>
+  </si>
+  <si>
+    <t>Size 'L' cho Nữ</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>Size 'XL' cho Nữ</t>
+  </si>
+  <si>
+    <t>XXL</t>
+  </si>
+  <si>
+    <t>Size 'XXL' cho Nữ</t>
+  </si>
+  <si>
+    <t>Size 'S' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'M' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'L' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'XL' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'XXL' cho Nam</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N1</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N2</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N3</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N4</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp N5</t>
+  </si>
+  <si>
+    <t>10.04.2026 08:10:20</t>
+  </si>
+  <si>
+    <t>12.04.2026 08:10:20</t>
+  </si>
+  <si>
+    <t>14.04.2026 08:10:20</t>
+  </si>
+  <si>
+    <t>16.04.2026 08:10:20</t>
+  </si>
+  <si>
+    <t>18.04.2026 08:10:20</t>
+  </si>
+  <si>
+    <t>20.04.2026 08:10:20</t>
+  </si>
+  <si>
+    <t>26.04.2026 08:10:20</t>
+  </si>
+  <si>
+    <t>28.04.2026 08:10:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thiếu C06_EMPLOYEE_ID =&gt; mỗi đơn hàng cần biết nhân viên nào tạo, xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Phí giao hàng C06_DELIVERY_FEE có thể chuyển sang T07_BILL, bỏ qua khi đơn hàng bị hủy</t>
+  </si>
+  <si>
+    <t>C07_DELIVERY_FEE</t>
+  </si>
+  <si>
+    <t>Với mỗi đơn hàng, tạo một hóa đơn [ngoại trừ 11, 12 bị hủy - thông tin hủy được lưu ở bảng tình trạng đơn hàng]
+- DELIVERY_FEE = random(20, 30, 40, 50)
+- TOTAL_OF_MONEY = 0 [dùng query xử lý khi thực hiện mua hàng]</t>
+  </si>
+  <si>
+    <t>Khách hàng 1</t>
+  </si>
+  <si>
+    <t>c1@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 1</t>
+  </si>
+  <si>
+    <t>$2a$12$w0bs0MW/O3nTyMhuv0r1jOjq2gOaxLxkZgms7u/khHRmtCh3S/Hpu</t>
+  </si>
+  <si>
+    <t>c1def</t>
+  </si>
+  <si>
+    <t>Khách hàng 2</t>
+  </si>
+  <si>
+    <t>c2@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 2</t>
+  </si>
+  <si>
+    <t>c2auto</t>
+  </si>
+  <si>
+    <t>Khách hàng 3</t>
+  </si>
+  <si>
+    <t>c3@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 3</t>
+  </si>
+  <si>
+    <t>c3def</t>
+  </si>
+  <si>
+    <t>Khách hàng 4</t>
+  </si>
+  <si>
+    <t>c4@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 4</t>
+  </si>
+  <si>
+    <t>c4auto</t>
+  </si>
+  <si>
+    <t>Khách hàng 5</t>
+  </si>
+  <si>
+    <t>c5@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 5</t>
+  </si>
+  <si>
+    <t>c5def</t>
+  </si>
+  <si>
+    <t>Khách hàng 6</t>
+  </si>
+  <si>
+    <t>c6@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 6</t>
+  </si>
+  <si>
+    <t>c6auto</t>
+  </si>
+  <si>
+    <t>Khách hàng 7</t>
+  </si>
+  <si>
+    <t>c7@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 7</t>
+  </si>
+  <si>
+    <t>c7def</t>
+  </si>
+  <si>
+    <t>Khách hàng 8</t>
+  </si>
+  <si>
+    <t>c8@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 8</t>
+  </si>
+  <si>
+    <t>c8auto</t>
+  </si>
+  <si>
+    <t>Khách hàng 9</t>
+  </si>
+  <si>
+    <t>c9@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 9</t>
+  </si>
+  <si>
+    <t>c9def</t>
+  </si>
+  <si>
+    <t>Khách hàng 10</t>
+  </si>
+  <si>
+    <t>c10@gmal.com</t>
+  </si>
+  <si>
+    <t>Địa chỉ 10</t>
+  </si>
+  <si>
+    <t>c10auto</t>
+  </si>
+  <si>
+    <t>sm1</t>
+  </si>
+  <si>
+    <t>sm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [Optional] bổ sung các thông tin về user/pass hỗ trợ đăng nhập</t>
+  </si>
+  <si>
+    <t>Nhân viên 1</t>
+  </si>
+  <si>
+    <t>nv1@gmail.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 2</t>
+  </si>
+  <si>
+    <t>nv2@gmail.com</t>
+  </si>
+  <si>
+    <t>Nhân viên 3</t>
+  </si>
+  <si>
+    <t>Nhân viên 4</t>
+  </si>
+  <si>
+    <t>Nhân viên 5</t>
+  </si>
+  <si>
+    <t>Nhân viên 6</t>
+  </si>
+  <si>
+    <t>Nhân viên 7</t>
+  </si>
+  <si>
+    <t>Nhân viên 8</t>
+  </si>
+  <si>
+    <t>Nhân viên 9</t>
+  </si>
+  <si>
+    <t>Nhân viên 10</t>
+  </si>
+  <si>
+    <t>Sử dụng ITEM ID từ bảng ITEM và fake default path
+format: file:///images/shopping/s_item_id.png</t>
+  </si>
+  <si>
+    <t>Fake 100 rows</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng ITEM, SIZE
+---
+ITEM, SIZE có ID lẻ: AMOUNT = 125, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5
+ITEM, SIZE có ID chẵn: AMOUNT = 280, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5 + 20</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng PROVIDER, ITEM
+---
+ITEM, PROVIDER có ID lẻ: AMOUNT = 777, BUY_PRICE =  random(50, 200)
+ITEM, WH có ID chẵn: AMOUNT = 820, BUY_PRICE =  random(100, 200)
+RECEIPT_DATE: sysdate - random(1, 4) days</t>
+  </si>
+  <si>
+    <t>-- 1. Đơn hàng từ 1 - 5 --&gt; Giao thành công (trạng thái từ 1 - 5)</t>
+  </si>
+  <si>
+    <t>-- 2 Đơn hàng từ 6 - 8 --&gt; Đóng gói thành công (trạng thái từ 1 - 3)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 2</t>
+  </si>
+  <si>
+    <t>-- 3. Đơn hàng từ 9 - 10 --&gt; Đang giao hàng (trạng thái từ 1 - 4)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 3</t>
+  </si>
+  <si>
+    <t>-- 4. Đơn hàng từ 11 - 12 --&gt; Hủy đơn hàng (trạng thái 7)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 4</t>
+  </si>
+  <si>
+    <t>-- 5. Đơn hàng từ 13  --&gt; Giao hàng thất bại (trạng thái 1,2,3,4,6)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 5</t>
+  </si>
+  <si>
+    <t>Tiền mặt</t>
+  </si>
+  <si>
+    <t>Thẻ tín dụng</t>
+  </si>
+  <si>
+    <t>Thẻ ghi nợ</t>
+  </si>
+  <si>
+    <t>Ví điện tử</t>
+  </si>
+  <si>
+    <t>Chờ xác nhận</t>
+  </si>
+  <si>
+    <t>Đóng gói hoàn thành</t>
+  </si>
+  <si>
+    <t>Đang vận chuyển</t>
+  </si>
+  <si>
+    <t>Giao hàng thất bại</t>
+  </si>
+  <si>
+    <t>Hủy đơn hàng</t>
+  </si>
+  <si>
+    <t>Địa chỉ 11</t>
+  </si>
+  <si>
+    <t>Địa chỉ 12</t>
+  </si>
+  <si>
+    <t>Địa chỉ 13</t>
+  </si>
+  <si>
+    <t>C06_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C06_ORDER+DATE + 5</t>
+  </si>
+  <si>
+    <t>Fake 50 rows</t>
+  </si>
+  <si>
+    <t>Với mỗi ITEM_GROUP
+- Nếu ID là số chẵn: tạo 2 SUB_ITEM_GROUP
+- Nếu ID là số lẻ: tạo 3 SUB_ITEM_GROUP
+=&gt; SIG_ID = ITEM_GROUP_ID + số bắt đầu từ 1
+=&gt; SIG_NAME = ITEM_GROUP_NAME + SIG_ID</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C06_DELIVERY_FEE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x</t>
+    </r>
+  </si>
+  <si>
+    <t>C07_TOTAL_OF_MONEY</t>
+  </si>
+  <si>
+    <t>SYSDATE - [max(ORDER_STATUS_ID) - ORDER_STATUS_Id]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2504,6 +3280,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -2543,7 +3326,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2612,11 +3395,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2819,6 +3662,30 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2826,6 +3693,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5540,10 +6443,10 @@
       <c r="B79" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C79" s="71" t="s">
+      <c r="C79" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="D79" s="72"/>
+      <c r="D79" s="80"/>
       <c r="E79" s="27"/>
       <c r="F79" s="27"/>
       <c r="G79" s="27"/>
@@ -6540,7 +7443,7 @@
       </c>
       <c r="F3" s="31"/>
       <c r="G3" s="27" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K3" s="31"/>
       <c r="L3" s="31"/>
@@ -6633,7 +7536,7 @@
         <v>313</v>
       </c>
       <c r="H6" s="61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I6" s="61" t="s">
         <v>299</v>
@@ -6654,13 +7557,13 @@
         <v>320</v>
       </c>
       <c r="O6" s="61" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P6" s="61" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q6" s="61" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6683,7 +7586,7 @@
         <v>314</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>301</v>
@@ -6704,13 +7607,13 @@
         <v>321</v>
       </c>
       <c r="O7" s="60" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P7" s="32" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="Q7" s="32" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6733,7 +7636,7 @@
         <v>316</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>302</v>
@@ -6754,13 +7657,13 @@
         <v>324</v>
       </c>
       <c r="O8" s="60" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P8" s="59" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q8" s="59" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6777,13 +7680,13 @@
         <v>267</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>326</v>
+        <v>499</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="I9" s="59" t="s">
         <v>303</v>
@@ -6802,7 +7705,7 @@
         <v>322</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
@@ -6837,7 +7740,7 @@
       </c>
       <c r="N10" s="35"/>
       <c r="O10" s="35" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="P10" s="35"/>
       <c r="Q10" s="35"/>
@@ -6903,7 +7806,7 @@
       <c r="E13" s="35"/>
       <c r="F13" s="35"/>
       <c r="G13" s="34" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="35" t="s">
@@ -7118,6 +8021,9 @@
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B27" s="54" t="s">
@@ -7149,7 +8055,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B30" s="56" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
@@ -7161,7 +8067,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B31" s="23" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -7169,7 +8075,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B32" s="23" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="23"/>
@@ -7193,7 +8099,7 @@
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" s="66" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C35" s="67"/>
       <c r="D35" s="67"/>
@@ -7203,19 +8109,19 @@
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" s="29" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I37" s="29"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B38" s="29" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I38" s="29"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
@@ -7405,8 +8311,8 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" s="31"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="70"/>
+      <c r="C81" s="78"/>
+      <c r="D81" s="78"/>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" s="50"/>
@@ -7775,4 +8681,3183 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4F83C2-F9A2-4590-A9AF-62EC0AAAB75B}">
+  <dimension ref="B1:R1000"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="20.7109375" style="26" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" style="26" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="26" customWidth="1"/>
+    <col min="8" max="8" width="26.5703125" style="26" customWidth="1"/>
+    <col min="9" max="9" width="30.7109375" style="26" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" style="26" customWidth="1"/>
+    <col min="11" max="11" width="26.28515625" style="26" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" style="26" customWidth="1"/>
+    <col min="13" max="15" width="20.7109375" style="26" customWidth="1"/>
+    <col min="16" max="16" width="23.5703125" style="26" customWidth="1"/>
+    <col min="17" max="17" width="23.42578125" style="26" customWidth="1"/>
+    <col min="18" max="39" width="20.7109375" style="26" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="61" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="H4" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>253</v>
+      </c>
+      <c r="N4" s="61" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" s="8">
+        <v>100</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="G5" s="8">
+        <v>11</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="K5" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="N5" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="O5" s="59" t="s">
+        <v>266</v>
+      </c>
+      <c r="P5" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q5" s="35" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8">
+        <v>2</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="D6" s="8">
+        <v>110</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="G6" s="8">
+        <v>11</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="J6" s="70">
+        <v>1</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="L6" s="70">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8">
+        <v>1</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="8">
+        <v>120</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="G7" s="8">
+        <v>12</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="70">
+        <v>2</v>
+      </c>
+      <c r="K7" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="L7" s="70">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8">
+        <v>2</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="8">
+        <v>130</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="G8" s="8">
+        <v>21</v>
+      </c>
+      <c r="H8" s="8">
+        <v>2</v>
+      </c>
+      <c r="J8" s="70">
+        <v>3</v>
+      </c>
+      <c r="K8" s="70" t="s">
+        <v>382</v>
+      </c>
+      <c r="L8" s="70">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8">
+        <v>3</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8">
+        <v>5</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D9" s="8">
+        <v>140</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="G9" s="8">
+        <v>21</v>
+      </c>
+      <c r="H9" s="8">
+        <v>2</v>
+      </c>
+      <c r="J9" s="70">
+        <v>4</v>
+      </c>
+      <c r="K9" s="70" t="s">
+        <v>383</v>
+      </c>
+      <c r="L9" s="70">
+        <v>1</v>
+      </c>
+      <c r="N9" s="8">
+        <v>4</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8">
+        <v>6</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D10" s="8">
+        <v>150</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="G10" s="8">
+        <v>31</v>
+      </c>
+      <c r="H10" s="8">
+        <v>3</v>
+      </c>
+      <c r="J10" s="70">
+        <v>5</v>
+      </c>
+      <c r="K10" s="70" t="s">
+        <v>154</v>
+      </c>
+      <c r="L10" s="70">
+        <v>1</v>
+      </c>
+      <c r="N10" s="8">
+        <v>5</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8">
+        <v>7</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="D11" s="8">
+        <v>160</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="G11" s="8">
+        <v>32</v>
+      </c>
+      <c r="H11" s="8">
+        <v>3</v>
+      </c>
+      <c r="J11" s="70">
+        <v>6</v>
+      </c>
+      <c r="K11" s="70" t="s">
+        <v>183</v>
+      </c>
+      <c r="L11" s="70">
+        <v>1</v>
+      </c>
+      <c r="N11" s="8">
+        <v>6</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P11" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8">
+        <v>8</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D12" s="8">
+        <v>170</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="G12" s="8">
+        <v>32</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="J12" s="70">
+        <v>7</v>
+      </c>
+      <c r="K12" s="70" t="s">
+        <v>384</v>
+      </c>
+      <c r="L12" s="70">
+        <v>1</v>
+      </c>
+      <c r="N12" s="8">
+        <v>7</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="D13" s="8">
+        <v>180</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="G13" s="8">
+        <v>33</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="N13" s="8">
+        <v>8</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="8">
+        <v>190</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="G14" s="8">
+        <v>31</v>
+      </c>
+      <c r="H14" s="8">
+        <v>3</v>
+      </c>
+      <c r="N14" s="8">
+        <v>9</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="P14" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8">
+        <v>11</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="D15" s="8">
+        <v>200</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="G15" s="8">
+        <v>41</v>
+      </c>
+      <c r="H15" s="8">
+        <v>4</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>254</v>
+      </c>
+      <c r="N15" s="8">
+        <v>10</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="P15" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8">
+        <v>12</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D16" s="8">
+        <v>210</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="G16" s="8">
+        <v>12</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="K16" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="L16" s="34" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8">
+        <v>13</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D17" s="8">
+        <v>220</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="G17" s="8">
+        <v>42</v>
+      </c>
+      <c r="H17" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8">
+        <v>14</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="D18" s="8">
+        <v>230</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8">
+        <v>5</v>
+      </c>
+      <c r="J18" s="81" t="s">
+        <v>498</v>
+      </c>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+    </row>
+    <row r="19" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8">
+        <v>15</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D19" s="8">
+        <v>240</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8">
+        <v>5</v>
+      </c>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+    </row>
+    <row r="20" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8">
+        <v>16</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D20" s="8">
+        <v>250</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="G20" s="8">
+        <v>61</v>
+      </c>
+      <c r="H20" s="8">
+        <v>6</v>
+      </c>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+    </row>
+    <row r="21" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8">
+        <v>17</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="D21" s="8">
+        <v>260</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8">
+        <v>6</v>
+      </c>
+      <c r="J21" s="81"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="81"/>
+    </row>
+    <row r="22" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="D22" s="8">
+        <v>270</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="G22" s="8">
+        <v>52</v>
+      </c>
+      <c r="H22" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8">
+        <v>19</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D23" s="8">
+        <v>280</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8">
+        <v>20</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="D24" s="8">
+        <v>290</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="G24" s="8">
+        <v>72</v>
+      </c>
+      <c r="H24" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="72" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="72" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="F27" s="61" t="s">
+        <v>313</v>
+      </c>
+      <c r="J27" s="76" t="s">
+        <v>496</v>
+      </c>
+      <c r="O27" s="77" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>349</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="G28" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="H28" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="I28" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="J28" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="K28" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="L28" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="M28" s="34" t="s">
+        <v>495</v>
+      </c>
+      <c r="O28" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="P28" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q28" s="35" t="s">
+        <v>500</v>
+      </c>
+      <c r="R28" s="35" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="70">
+        <v>1</v>
+      </c>
+      <c r="C29" s="70" t="s">
+        <v>397</v>
+      </c>
+      <c r="D29" s="70">
+        <v>11</v>
+      </c>
+      <c r="F29" s="8">
+        <v>1</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="H29" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I29" s="71" t="s">
+        <v>402</v>
+      </c>
+      <c r="J29" s="73"/>
+      <c r="K29" s="8">
+        <v>1</v>
+      </c>
+      <c r="L29" s="8">
+        <v>1</v>
+      </c>
+      <c r="M29" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="70">
+        <v>2</v>
+      </c>
+      <c r="C30" s="70" t="s">
+        <v>398</v>
+      </c>
+      <c r="D30" s="70">
+        <v>12</v>
+      </c>
+      <c r="F30" s="8">
+        <v>2</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H30" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I30" s="71" t="s">
+        <v>403</v>
+      </c>
+      <c r="J30" s="73"/>
+      <c r="K30" s="8">
+        <v>1</v>
+      </c>
+      <c r="L30" s="8">
+        <v>2</v>
+      </c>
+      <c r="M30" s="8">
+        <v>8</v>
+      </c>
+      <c r="O30" s="82" t="s">
+        <v>413</v>
+      </c>
+      <c r="P30" s="83"/>
+      <c r="Q30" s="84"/>
+    </row>
+    <row r="31" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="70">
+        <v>3</v>
+      </c>
+      <c r="C31" s="70" t="s">
+        <v>399</v>
+      </c>
+      <c r="D31" s="70">
+        <v>13</v>
+      </c>
+      <c r="F31" s="8">
+        <v>3</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="H31" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I31" s="71" t="s">
+        <v>404</v>
+      </c>
+      <c r="J31" s="73"/>
+      <c r="K31" s="8">
+        <v>2</v>
+      </c>
+      <c r="L31" s="8">
+        <v>3</v>
+      </c>
+      <c r="M31" s="8">
+        <v>9</v>
+      </c>
+      <c r="O31" s="85"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="87"/>
+    </row>
+    <row r="32" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="70">
+        <v>4</v>
+      </c>
+      <c r="C32" s="70" t="s">
+        <v>400</v>
+      </c>
+      <c r="D32" s="70">
+        <v>14</v>
+      </c>
+      <c r="F32" s="8">
+        <v>4</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="H32" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I32" s="71" t="s">
+        <v>405</v>
+      </c>
+      <c r="J32" s="73"/>
+      <c r="K32" s="8">
+        <v>3</v>
+      </c>
+      <c r="L32" s="8">
+        <v>4</v>
+      </c>
+      <c r="M32" s="8">
+        <v>10</v>
+      </c>
+      <c r="O32" s="85"/>
+      <c r="P32" s="86"/>
+      <c r="Q32" s="87"/>
+    </row>
+    <row r="33" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="70">
+        <v>5</v>
+      </c>
+      <c r="C33" s="70" t="s">
+        <v>401</v>
+      </c>
+      <c r="D33" s="70">
+        <v>15</v>
+      </c>
+      <c r="F33" s="8">
+        <v>5</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="H33" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I33" s="71" t="s">
+        <v>406</v>
+      </c>
+      <c r="J33" s="73"/>
+      <c r="K33" s="8">
+        <v>4</v>
+      </c>
+      <c r="L33" s="8">
+        <v>5</v>
+      </c>
+      <c r="M33" s="8">
+        <v>8</v>
+      </c>
+      <c r="O33" s="88"/>
+      <c r="P33" s="89"/>
+      <c r="Q33" s="90"/>
+    </row>
+    <row r="34" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="8">
+        <v>6</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="H34" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I34" s="71" t="s">
+        <v>403</v>
+      </c>
+      <c r="J34" s="73"/>
+      <c r="K34" s="8">
+        <v>3</v>
+      </c>
+      <c r="L34" s="8">
+        <v>6</v>
+      </c>
+      <c r="M34" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="8">
+        <v>7</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H35" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I35" s="71" t="s">
+        <v>404</v>
+      </c>
+      <c r="J35" s="73"/>
+      <c r="K35" s="8">
+        <v>2</v>
+      </c>
+      <c r="L35" s="8">
+        <v>7</v>
+      </c>
+      <c r="M35" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="8">
+        <v>8</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="H36" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I36" s="71" t="s">
+        <v>406</v>
+      </c>
+      <c r="J36" s="73"/>
+      <c r="K36" s="8">
+        <v>1</v>
+      </c>
+      <c r="L36" s="8">
+        <v>8</v>
+      </c>
+      <c r="M36" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="8">
+        <v>9</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="H37" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I37" s="71" t="s">
+        <v>406</v>
+      </c>
+      <c r="J37" s="73"/>
+      <c r="K37" s="8">
+        <v>4</v>
+      </c>
+      <c r="L37" s="8">
+        <v>9</v>
+      </c>
+      <c r="M37" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="8">
+        <v>10</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="H38" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I38" s="71" t="s">
+        <v>406</v>
+      </c>
+      <c r="J38" s="73"/>
+      <c r="K38" s="8">
+        <v>4</v>
+      </c>
+      <c r="L38" s="8">
+        <v>10</v>
+      </c>
+      <c r="M38" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F39" s="8">
+        <v>11</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H39" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I39" s="71" t="s">
+        <v>407</v>
+      </c>
+      <c r="J39" s="73"/>
+      <c r="K39" s="8">
+        <v>3</v>
+      </c>
+      <c r="L39" s="8">
+        <v>2</v>
+      </c>
+      <c r="M39" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F40" s="8">
+        <v>12</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="H40" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I40" s="71" t="s">
+        <v>408</v>
+      </c>
+      <c r="J40" s="73"/>
+      <c r="K40" s="8">
+        <v>2</v>
+      </c>
+      <c r="L40" s="8">
+        <v>4</v>
+      </c>
+      <c r="M40" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F41" s="8">
+        <v>13</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="H41" s="8">
+        <v>123459789</v>
+      </c>
+      <c r="I41" s="71" t="s">
+        <v>409</v>
+      </c>
+      <c r="J41" s="73"/>
+      <c r="K41" s="8">
+        <v>1</v>
+      </c>
+      <c r="L41" s="8">
+        <v>6</v>
+      </c>
+      <c r="M41" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="61" t="s">
+        <v>299</v>
+      </c>
+      <c r="K44" s="61" t="s">
+        <v>300</v>
+      </c>
+      <c r="L44" s="72" t="s">
+        <v>457</v>
+      </c>
+      <c r="P44" s="61" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="D45" s="59" t="s">
+        <v>303</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="G45" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="H45" s="35" t="s">
+        <v>305</v>
+      </c>
+      <c r="I45" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="K45" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="L45" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="M45" s="59" t="s">
+        <v>311</v>
+      </c>
+      <c r="N45" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="P45" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q45" s="32" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="8">
+        <v>1</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="D46" s="71" t="s">
+        <v>415</v>
+      </c>
+      <c r="E46" s="8">
+        <v>123456789</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="G46" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="K46" s="8">
+        <v>1</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="M46" s="71" t="s">
+        <v>459</v>
+      </c>
+      <c r="N46" s="8">
+        <v>123456789</v>
+      </c>
+      <c r="P46" s="91" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q46" s="92"/>
+    </row>
+    <row r="47" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="8">
+        <v>2</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="E47" s="8">
+        <v>223456789</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="G47" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="K47" s="8">
+        <v>2</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="N47" s="8">
+        <v>223456789</v>
+      </c>
+      <c r="P47" s="92"/>
+      <c r="Q47" s="92"/>
+    </row>
+    <row r="48" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="8">
+        <v>3</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="E48" s="8">
+        <v>323456789</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="G48" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="K48" s="8">
+        <v>3</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="M48" s="71" t="s">
+        <v>459</v>
+      </c>
+      <c r="N48" s="8">
+        <v>323456789</v>
+      </c>
+      <c r="P48" s="92"/>
+      <c r="Q48" s="92"/>
+    </row>
+    <row r="49" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="8">
+        <v>4</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="E49" s="8">
+        <v>423456789</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="G49" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="K49" s="8">
+        <v>4</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="N49" s="8">
+        <v>423456789</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="8">
+        <v>5</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="E50" s="8">
+        <v>523456789</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="G50" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="K50" s="8">
+        <v>5</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="M50" s="71" t="s">
+        <v>459</v>
+      </c>
+      <c r="N50" s="8">
+        <v>523456789</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="8">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="E51" s="8">
+        <v>623456789</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="G51" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="K51" s="8">
+        <v>6</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="N51" s="8">
+        <v>623456789</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="8">
+        <v>7</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="E52" s="8">
+        <v>723456789</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G52" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="K52" s="8">
+        <v>7</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="M52" s="71" t="s">
+        <v>459</v>
+      </c>
+      <c r="N52" s="8">
+        <v>723456789</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="8">
+        <v>8</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E53" s="8">
+        <v>823456789</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G53" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="K53" s="8">
+        <v>8</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="N53" s="8">
+        <v>823456789</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="8">
+        <v>9</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="E54" s="8">
+        <v>923456789</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="G54" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="K54" s="8">
+        <v>9</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="M54" s="71" t="s">
+        <v>459</v>
+      </c>
+      <c r="N54" s="8">
+        <v>923456789</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="8">
+        <v>10</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E55" s="8">
+        <v>1023456789</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="G55" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="K55" s="8">
+        <v>10</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="N55" s="8">
+        <v>1023456789</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="H58" s="61" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="C59" s="62" t="s">
+        <v>270</v>
+      </c>
+      <c r="D59" s="62" t="s">
+        <v>271</v>
+      </c>
+      <c r="E59" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="F59" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="H59" s="60" t="s">
+        <v>285</v>
+      </c>
+      <c r="I59" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="J59" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="K59" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="L59" s="35" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="H60" s="9" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="91" t="s">
+        <v>472</v>
+      </c>
+      <c r="C61" s="91"/>
+      <c r="D61" s="91"/>
+      <c r="E61" s="91"/>
+      <c r="F61" s="91"/>
+      <c r="H61" s="91" t="s">
+        <v>473</v>
+      </c>
+      <c r="I61" s="91"/>
+      <c r="J61" s="91"/>
+      <c r="K61" s="91"/>
+      <c r="L61" s="91"/>
+    </row>
+    <row r="62" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="91"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="91"/>
+      <c r="E62" s="91"/>
+      <c r="F62" s="91"/>
+      <c r="H62" s="91"/>
+      <c r="I62" s="91"/>
+      <c r="J62" s="91"/>
+      <c r="K62" s="91"/>
+      <c r="L62" s="91"/>
+    </row>
+    <row r="63" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="91"/>
+      <c r="C63" s="91"/>
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
+      <c r="F63" s="91"/>
+      <c r="H63" s="91"/>
+      <c r="I63" s="91"/>
+      <c r="J63" s="91"/>
+      <c r="K63" s="91"/>
+      <c r="L63" s="91"/>
+    </row>
+    <row r="64" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="91"/>
+      <c r="C64" s="91"/>
+      <c r="D64" s="91"/>
+      <c r="E64" s="91"/>
+      <c r="F64" s="91"/>
+      <c r="H64" s="91"/>
+      <c r="I64" s="91"/>
+      <c r="J64" s="91"/>
+      <c r="K64" s="91"/>
+      <c r="L64" s="91"/>
+    </row>
+    <row r="65" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="61" t="s">
+        <v>320</v>
+      </c>
+      <c r="H67" s="77" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="60" t="s">
+        <v>321</v>
+      </c>
+      <c r="C68" s="60" t="s">
+        <v>324</v>
+      </c>
+      <c r="D68" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="H68" s="60" t="s">
+        <v>338</v>
+      </c>
+      <c r="I68" s="60" t="s">
+        <v>339</v>
+      </c>
+      <c r="J68" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="K68" s="35" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="8">
+        <v>1</v>
+      </c>
+      <c r="C69" s="8">
+        <v>1</v>
+      </c>
+      <c r="D69" s="8">
+        <v>2</v>
+      </c>
+      <c r="H69" s="75" t="s">
+        <v>474</v>
+      </c>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="L69"/>
+    </row>
+    <row r="70" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="8">
+        <v>1</v>
+      </c>
+      <c r="C70" s="8">
+        <v>3</v>
+      </c>
+      <c r="D70" s="8">
+        <v>4</v>
+      </c>
+      <c r="H70" s="75" t="s">
+        <v>475</v>
+      </c>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K70" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="L70"/>
+    </row>
+    <row r="71" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="8">
+        <v>2</v>
+      </c>
+      <c r="C71" s="8">
+        <v>4</v>
+      </c>
+      <c r="D71" s="8">
+        <v>2</v>
+      </c>
+      <c r="H71" s="75" t="s">
+        <v>477</v>
+      </c>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="K71" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="L71"/>
+    </row>
+    <row r="72" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="8">
+        <v>2</v>
+      </c>
+      <c r="C72" s="8">
+        <v>5</v>
+      </c>
+      <c r="D72" s="8">
+        <v>2</v>
+      </c>
+      <c r="H72" s="75" t="s">
+        <v>479</v>
+      </c>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="K72" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="L72"/>
+    </row>
+    <row r="73" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="8">
+        <v>3</v>
+      </c>
+      <c r="C73" s="8">
+        <v>6</v>
+      </c>
+      <c r="D73" s="8">
+        <v>4</v>
+      </c>
+      <c r="H73" s="75" t="s">
+        <v>481</v>
+      </c>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="K73" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="L73"/>
+    </row>
+    <row r="74" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="8">
+        <v>3</v>
+      </c>
+      <c r="C74" s="8">
+        <v>2</v>
+      </c>
+      <c r="D74" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="8">
+        <v>4</v>
+      </c>
+      <c r="C75" s="8">
+        <v>8</v>
+      </c>
+      <c r="D75" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="8">
+        <v>4</v>
+      </c>
+      <c r="C76" s="8">
+        <v>12</v>
+      </c>
+      <c r="D76" s="8">
+        <v>4</v>
+      </c>
+      <c r="H76" s="61" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="8">
+        <v>5</v>
+      </c>
+      <c r="C77" s="8">
+        <v>88</v>
+      </c>
+      <c r="D77" s="8">
+        <v>1</v>
+      </c>
+      <c r="H77" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="I77" s="59" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="8">
+        <v>5</v>
+      </c>
+      <c r="C78" s="8">
+        <v>22</v>
+      </c>
+      <c r="D78" s="8">
+        <v>3</v>
+      </c>
+      <c r="H78" s="8">
+        <v>1</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="8">
+        <v>5</v>
+      </c>
+      <c r="C79" s="8">
+        <v>11</v>
+      </c>
+      <c r="D79" s="8">
+        <v>1</v>
+      </c>
+      <c r="H79" s="8">
+        <v>2</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="8">
+        <v>5</v>
+      </c>
+      <c r="C80" s="8">
+        <v>33</v>
+      </c>
+      <c r="D80" s="8">
+        <v>1</v>
+      </c>
+      <c r="H80" s="8">
+        <v>3</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="8">
+        <v>6</v>
+      </c>
+      <c r="C81" s="8">
+        <v>2</v>
+      </c>
+      <c r="D81" s="8">
+        <v>1</v>
+      </c>
+      <c r="H81" s="8">
+        <v>4</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="8">
+        <v>7</v>
+      </c>
+      <c r="C82" s="8">
+        <v>1</v>
+      </c>
+      <c r="D82" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="8">
+        <v>8</v>
+      </c>
+      <c r="C83" s="8">
+        <v>27</v>
+      </c>
+      <c r="D83" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="8">
+        <v>8</v>
+      </c>
+      <c r="C84" s="8">
+        <v>23</v>
+      </c>
+      <c r="D84" s="8">
+        <v>1</v>
+      </c>
+      <c r="H84" s="61" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="8">
+        <v>8</v>
+      </c>
+      <c r="C85" s="8">
+        <v>98</v>
+      </c>
+      <c r="D85" s="8">
+        <v>2</v>
+      </c>
+      <c r="H85" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="I85" s="59" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="8">
+        <v>9</v>
+      </c>
+      <c r="C86" s="8">
+        <v>100</v>
+      </c>
+      <c r="D86" s="8">
+        <v>6</v>
+      </c>
+      <c r="H86" s="8">
+        <v>1</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="8">
+        <v>9</v>
+      </c>
+      <c r="C87" s="8">
+        <v>11</v>
+      </c>
+      <c r="D87" s="8">
+        <v>7</v>
+      </c>
+      <c r="H87" s="8">
+        <v>2</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="8">
+        <v>9</v>
+      </c>
+      <c r="C88" s="8">
+        <v>45</v>
+      </c>
+      <c r="D88" s="8">
+        <v>2</v>
+      </c>
+      <c r="H88" s="8">
+        <v>3</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="8">
+        <v>9</v>
+      </c>
+      <c r="C89" s="8">
+        <v>22</v>
+      </c>
+      <c r="D89" s="8">
+        <v>2</v>
+      </c>
+      <c r="H89" s="8">
+        <v>4</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="8">
+        <v>9</v>
+      </c>
+      <c r="C90" s="8">
+        <v>32</v>
+      </c>
+      <c r="D90" s="8">
+        <v>1</v>
+      </c>
+      <c r="H90" s="8">
+        <v>5</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="8">
+        <v>10</v>
+      </c>
+      <c r="C91" s="8">
+        <v>18</v>
+      </c>
+      <c r="D91" s="8">
+        <v>2</v>
+      </c>
+      <c r="H91" s="8">
+        <v>6</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="8">
+        <v>10</v>
+      </c>
+      <c r="C92" s="8">
+        <v>29</v>
+      </c>
+      <c r="D92" s="8">
+        <v>4</v>
+      </c>
+      <c r="H92" s="8">
+        <v>7</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="8">
+        <v>11</v>
+      </c>
+      <c r="C93" s="8">
+        <v>33</v>
+      </c>
+      <c r="D93" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="8">
+        <v>11</v>
+      </c>
+      <c r="C94" s="8">
+        <v>65</v>
+      </c>
+      <c r="D94" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="8">
+        <v>11</v>
+      </c>
+      <c r="C95" s="8">
+        <v>1</v>
+      </c>
+      <c r="D95" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="8">
+        <v>11</v>
+      </c>
+      <c r="C96" s="8">
+        <v>2</v>
+      </c>
+      <c r="D96" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="8">
+        <v>11</v>
+      </c>
+      <c r="C97" s="8">
+        <v>5</v>
+      </c>
+      <c r="D97" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="8">
+        <v>11</v>
+      </c>
+      <c r="C98" s="8">
+        <v>7</v>
+      </c>
+      <c r="D98" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="8">
+        <v>12</v>
+      </c>
+      <c r="C99" s="8">
+        <v>55</v>
+      </c>
+      <c r="D99" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="8">
+        <v>13</v>
+      </c>
+      <c r="C100" s="8">
+        <v>92</v>
+      </c>
+      <c r="D100" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="8">
+        <v>13</v>
+      </c>
+      <c r="C101" s="8">
+        <v>14</v>
+      </c>
+      <c r="D101" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="J18:L21"/>
+    <mergeCell ref="O30:Q33"/>
+    <mergeCell ref="P46:Q48"/>
+    <mergeCell ref="B61:F64"/>
+    <mergeCell ref="H61:L64"/>
+  </mergeCells>
+  <phoneticPr fontId="25" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/1. Database Design/Java25 Quyen Phan Database Design.xlsx
+++ b/1. Database Design/Java25 Quyen Phan Database Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java25\3. Database\1. Database Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070D2665-7CA5-4612-8AD4-8471397BB613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2C0820-E7B1-40E7-9819-FCA89B98F114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1860" windowWidth="38640" windowHeight="21120" tabRatio="588" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="588" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -3686,15 +3686,6 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3729,6 +3720,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6443,10 +6443,10 @@
       <c r="B79" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C79" s="79" t="s">
+      <c r="C79" s="90" t="s">
         <v>178</v>
       </c>
-      <c r="D79" s="80"/>
+      <c r="D79" s="91"/>
       <c r="E79" s="27"/>
       <c r="F79" s="27"/>
       <c r="G79" s="27"/>
@@ -8311,8 +8311,8 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" s="31"/>
-      <c r="C81" s="78"/>
-      <c r="D81" s="78"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" s="50"/>
@@ -9270,11 +9270,11 @@
       <c r="H18" s="8">
         <v>5</v>
       </c>
-      <c r="J18" s="81" t="s">
+      <c r="J18" s="78" t="s">
         <v>498</v>
       </c>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="8">
@@ -9296,9 +9296,9 @@
       <c r="H19" s="8">
         <v>5</v>
       </c>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="8">
@@ -9322,9 +9322,9 @@
       <c r="H20" s="8">
         <v>6</v>
       </c>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="8">
@@ -9346,9 +9346,9 @@
       <c r="H21" s="8">
         <v>6</v>
       </c>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="8">
@@ -9553,11 +9553,11 @@
       <c r="M30" s="8">
         <v>8</v>
       </c>
-      <c r="O30" s="82" t="s">
+      <c r="O30" s="79" t="s">
         <v>413</v>
       </c>
-      <c r="P30" s="83"/>
-      <c r="Q30" s="84"/>
+      <c r="P30" s="80"/>
+      <c r="Q30" s="81"/>
     </row>
     <row r="31" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="70">
@@ -9591,9 +9591,9 @@
       <c r="M31" s="8">
         <v>9</v>
       </c>
-      <c r="O31" s="85"/>
-      <c r="P31" s="86"/>
-      <c r="Q31" s="87"/>
+      <c r="O31" s="82"/>
+      <c r="P31" s="83"/>
+      <c r="Q31" s="84"/>
     </row>
     <row r="32" spans="2:18" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="70">
@@ -9627,9 +9627,9 @@
       <c r="M32" s="8">
         <v>10</v>
       </c>
-      <c r="O32" s="85"/>
-      <c r="P32" s="86"/>
-      <c r="Q32" s="87"/>
+      <c r="O32" s="82"/>
+      <c r="P32" s="83"/>
+      <c r="Q32" s="84"/>
     </row>
     <row r="33" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="70">
@@ -9663,9 +9663,9 @@
       <c r="M33" s="8">
         <v>8</v>
       </c>
-      <c r="O33" s="88"/>
-      <c r="P33" s="89"/>
-      <c r="Q33" s="90"/>
+      <c r="O33" s="85"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="87"/>
     </row>
     <row r="34" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F34" s="8">
@@ -9956,10 +9956,10 @@
       <c r="N46" s="8">
         <v>123456789</v>
       </c>
-      <c r="P46" s="91" t="s">
+      <c r="P46" s="88" t="s">
         <v>470</v>
       </c>
-      <c r="Q46" s="92"/>
+      <c r="Q46" s="89"/>
     </row>
     <row r="47" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="8">
@@ -9998,8 +9998,8 @@
       <c r="N47" s="8">
         <v>223456789</v>
       </c>
-      <c r="P47" s="92"/>
-      <c r="Q47" s="92"/>
+      <c r="P47" s="89"/>
+      <c r="Q47" s="89"/>
     </row>
     <row r="48" spans="2:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="8">
@@ -10038,8 +10038,8 @@
       <c r="N48" s="8">
         <v>323456789</v>
       </c>
-      <c r="P48" s="92"/>
-      <c r="Q48" s="92"/>
+      <c r="P48" s="89"/>
+      <c r="Q48" s="89"/>
     </row>
     <row r="49" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="8">
@@ -10362,56 +10362,56 @@
       </c>
     </row>
     <row r="61" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="91" t="s">
+      <c r="B61" s="88" t="s">
         <v>472</v>
       </c>
-      <c r="C61" s="91"/>
-      <c r="D61" s="91"/>
-      <c r="E61" s="91"/>
-      <c r="F61" s="91"/>
-      <c r="H61" s="91" t="s">
+      <c r="C61" s="88"/>
+      <c r="D61" s="88"/>
+      <c r="E61" s="88"/>
+      <c r="F61" s="88"/>
+      <c r="H61" s="88" t="s">
         <v>473</v>
       </c>
-      <c r="I61" s="91"/>
-      <c r="J61" s="91"/>
-      <c r="K61" s="91"/>
-      <c r="L61" s="91"/>
+      <c r="I61" s="88"/>
+      <c r="J61" s="88"/>
+      <c r="K61" s="88"/>
+      <c r="L61" s="88"/>
     </row>
     <row r="62" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="91"/>
-      <c r="C62" s="91"/>
-      <c r="D62" s="91"/>
-      <c r="E62" s="91"/>
-      <c r="F62" s="91"/>
-      <c r="H62" s="91"/>
-      <c r="I62" s="91"/>
-      <c r="J62" s="91"/>
-      <c r="K62" s="91"/>
-      <c r="L62" s="91"/>
+      <c r="B62" s="88"/>
+      <c r="C62" s="88"/>
+      <c r="D62" s="88"/>
+      <c r="E62" s="88"/>
+      <c r="F62" s="88"/>
+      <c r="H62" s="88"/>
+      <c r="I62" s="88"/>
+      <c r="J62" s="88"/>
+      <c r="K62" s="88"/>
+      <c r="L62" s="88"/>
     </row>
     <row r="63" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="91"/>
-      <c r="C63" s="91"/>
-      <c r="D63" s="91"/>
-      <c r="E63" s="91"/>
-      <c r="F63" s="91"/>
-      <c r="H63" s="91"/>
-      <c r="I63" s="91"/>
-      <c r="J63" s="91"/>
-      <c r="K63" s="91"/>
-      <c r="L63" s="91"/>
+      <c r="B63" s="88"/>
+      <c r="C63" s="88"/>
+      <c r="D63" s="88"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="88"/>
+      <c r="H63" s="88"/>
+      <c r="I63" s="88"/>
+      <c r="J63" s="88"/>
+      <c r="K63" s="88"/>
+      <c r="L63" s="88"/>
     </row>
     <row r="64" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="91"/>
-      <c r="C64" s="91"/>
-      <c r="D64" s="91"/>
-      <c r="E64" s="91"/>
-      <c r="F64" s="91"/>
-      <c r="H64" s="91"/>
-      <c r="I64" s="91"/>
-      <c r="J64" s="91"/>
-      <c r="K64" s="91"/>
-      <c r="L64" s="91"/>
+      <c r="B64" s="88"/>
+      <c r="C64" s="88"/>
+      <c r="D64" s="88"/>
+      <c r="E64" s="88"/>
+      <c r="F64" s="88"/>
+      <c r="H64" s="88"/>
+      <c r="I64" s="88"/>
+      <c r="J64" s="88"/>
+      <c r="K64" s="88"/>
+      <c r="L64" s="88"/>
     </row>
     <row r="65" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" spans="2:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
